--- a/Assets/Excel/OpenBox.xlsx
+++ b/Assets/Excel/OpenBox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF02DEB-5DAC-4B81-8902-EFCEAAEE6BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C101EDC-885C-4936-9BBF-B000395D05B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,6 +85,42 @@
   </si>
   <si>
     <t>Rare6Weight</t>
+  </si>
+  <si>
+    <t>品质名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RareName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>粗糙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史诗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传世</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -424,56 +460,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
-    <col min="2" max="7" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="10.25" style="2" customWidth="1"/>
+    <col min="3" max="8" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -490,43 +529,49 @@
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2">
         <v>90</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>10</v>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
@@ -537,26 +582,29 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <f>SUM(B4:G4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <f>SUM(C4:H4)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2">
         <v>80</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>15</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>5</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
@@ -564,114 +612,129 @@
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" ref="H5:H9" si="0">SUM(B5:G5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" ref="I5:I9" si="0">SUM(C5:H5)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>25</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>15</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>9</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
       <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
-        <v>20</v>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>20</v>
       </c>
       <c r="D7" s="2">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
         <v>40</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>9</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
       </c>
       <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>40</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>20</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>30</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>10</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
       </c>
       <c r="F9" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
       </c>
       <c r="H9" s="2">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
